--- a/output/Data and Chart Outputs/oil_cost_curve.xlsx
+++ b/output/Data and Chart Outputs/oil_cost_curve.xlsx
@@ -4014,10 +4014,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>-66.22617992</t>
-        </is>
+      <c r="D2" t="n">
+        <v>-66.22617992000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4046,10 +4044,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>-64.31499151</t>
-        </is>
+      <c r="D3" t="n">
+        <v>-64.31499151</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -4078,10 +4074,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>-61.90378453</t>
-        </is>
+      <c r="D4" t="n">
+        <v>-61.90378453</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -4110,10 +4104,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>-60.84300047</t>
-        </is>
+      <c r="D5" t="n">
+        <v>-60.84300047</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -4142,10 +4134,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>-61.65699664</t>
-        </is>
+      <c r="D6" t="n">
+        <v>-61.65699664</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -4174,10 +4164,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>-63.24702789</t>
-        </is>
+      <c r="D7" t="n">
+        <v>-63.24702789</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -4206,10 +4194,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>-65.00153383</t>
-        </is>
+      <c r="D8" t="n">
+        <v>-65.00153383</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -4238,10 +4224,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>-68.09203165</t>
-        </is>
+      <c r="D9" t="n">
+        <v>-68.09203165</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -4270,10 +4254,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>-70.30650167</t>
-        </is>
+      <c r="D10" t="n">
+        <v>-70.30650167</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -4302,10 +4284,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>-71.16792535</t>
-        </is>
+      <c r="D11" t="n">
+        <v>-71.16792535</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -4334,10 +4314,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>-71.25007571</t>
-        </is>
+      <c r="D12" t="n">
+        <v>-71.25007571</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -4366,10 +4344,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>-70.07115209</t>
-        </is>
+      <c r="D13" t="n">
+        <v>-70.07115209</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -4398,10 +4374,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>-69.70807409</t>
-        </is>
+      <c r="D14" t="n">
+        <v>-69.70807409</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -4430,10 +4404,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-70.05161526</t>
-        </is>
+      <c r="D15" t="n">
+        <v>-70.05161526000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -4462,10 +4434,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>-69.75271234</t>
-        </is>
+      <c r="D16" t="n">
+        <v>-69.75271234</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -4494,10 +4464,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>-69.62894099</t>
-        </is>
+      <c r="D17" t="n">
+        <v>-69.62894099</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -4526,10 +4494,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>-69.66575738</t>
-        </is>
+      <c r="D18" t="n">
+        <v>-69.66575738</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -4558,10 +4524,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>-70.06651797</t>
-        </is>
+      <c r="D19" t="n">
+        <v>-70.06651797000001</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -4590,10 +4554,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>-70.79015763</t>
-        </is>
+      <c r="D20" t="n">
+        <v>-70.79015763</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -4622,10 +4584,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>-71.79397539</t>
-        </is>
+      <c r="D21" t="n">
+        <v>-71.79397539</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4654,10 +4614,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>-77.10255633</t>
-        </is>
+      <c r="D22" t="n">
+        <v>-77.10255633</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -4686,10 +4644,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>-76.14322</t>
-        </is>
+      <c r="D23" t="n">
+        <v>-76.14322</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -4718,10 +4674,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>-75.03103644</t>
-        </is>
+      <c r="D24" t="n">
+        <v>-75.03103643999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -4750,10 +4704,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>-75.4010382</t>
-        </is>
+      <c r="D25" t="n">
+        <v>-75.4010382</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -4782,10 +4734,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>-78.41416328</t>
-        </is>
+      <c r="D26" t="n">
+        <v>-78.41416328</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -4814,10 +4764,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>-82.68678771</t>
-        </is>
+      <c r="D27" t="n">
+        <v>-82.68678771</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4846,10 +4794,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>-85.84168148</t>
-        </is>
+      <c r="D28" t="n">
+        <v>-85.84168148000001</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -4878,10 +4824,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>-86.2742891</t>
-        </is>
+      <c r="D29" t="n">
+        <v>-86.2742891</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -4910,10 +4854,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>-85.72994744</t>
-        </is>
+      <c r="D30" t="n">
+        <v>-85.72994744</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -4942,10 +4884,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>-84.60841997</t>
-        </is>
+      <c r="D31" t="n">
+        <v>-84.60841997</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -4974,10 +4914,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>-83.29726218</t>
-        </is>
+      <c r="D32" t="n">
+        <v>-83.29726218</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -5006,10 +4944,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>-81.52239624</t>
-        </is>
+      <c r="D33" t="n">
+        <v>-81.52239624000001</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -5038,10 +4974,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>-79.4016371</t>
-        </is>
+      <c r="D34" t="n">
+        <v>-79.4016371</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -5070,10 +5004,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>-79.04763219</t>
-        </is>
+      <c r="D35" t="n">
+        <v>-79.04763219</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -5102,10 +5034,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-80.42465404</t>
-        </is>
+      <c r="D36" t="n">
+        <v>-80.42465403999999</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -5134,10 +5064,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>-81.68274144</t>
-        </is>
+      <c r="D37" t="n">
+        <v>-81.68274144</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -5166,10 +5094,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>-82.79247504</t>
-        </is>
+      <c r="D38" t="n">
+        <v>-82.79247504</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -5198,10 +5124,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>-83.82943195</t>
-        </is>
+      <c r="D39" t="n">
+        <v>-83.82943195</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -5230,10 +5154,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>-84.73232527</t>
-        </is>
+      <c r="D40" t="n">
+        <v>-84.73232527</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -5262,10 +5184,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>-85.57281183</t>
-        </is>
+      <c r="D41" t="n">
+        <v>-85.57281183000001</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -5294,10 +5214,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>-431.8810585</t>
-        </is>
+      <c r="D42" t="n">
+        <v>-431.8810585</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -5326,10 +5244,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>-437.2248584</t>
-        </is>
+      <c r="D43" t="n">
+        <v>-437.2248584</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -5358,10 +5274,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>-437.0535679</t>
-        </is>
+      <c r="D44" t="n">
+        <v>-437.0535679</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -5390,10 +5304,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>-430.0453715</t>
-        </is>
+      <c r="D45" t="n">
+        <v>-430.0453715</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -5422,10 +5334,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>-424.1256063</t>
-        </is>
+      <c r="D46" t="n">
+        <v>-424.1256063</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -5454,10 +5364,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>-423.5037347</t>
-        </is>
+      <c r="D47" t="n">
+        <v>-423.5037347</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -5486,10 +5394,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>-427.617813</t>
-        </is>
+      <c r="D48" t="n">
+        <v>-427.617813</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -5518,10 +5424,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>-433.8027777</t>
-        </is>
+      <c r="D49" t="n">
+        <v>-433.8027777</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -5550,10 +5454,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>-443.9456071</t>
-        </is>
+      <c r="D50" t="n">
+        <v>-443.9456071</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -5582,10 +5484,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>-450.0002832</t>
-        </is>
+      <c r="D51" t="n">
+        <v>-450.0002832</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -5614,10 +5514,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>-453.7307433</t>
-        </is>
+      <c r="D52" t="n">
+        <v>-453.7307433</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -5646,10 +5544,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>-456.3802819</t>
-        </is>
+      <c r="D53" t="n">
+        <v>-456.3802819</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -5678,10 +5574,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>-458.7776818</t>
-        </is>
+      <c r="D54" t="n">
+        <v>-458.7776818</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -5710,10 +5604,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>-460.3982172</t>
-        </is>
+      <c r="D55" t="n">
+        <v>-460.3982172</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -5742,10 +5634,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>-458.3953519</t>
-        </is>
+      <c r="D56" t="n">
+        <v>-458.3953519</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -5774,10 +5664,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>-461.5852785</t>
-        </is>
+      <c r="D57" t="n">
+        <v>-461.5852785</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -5806,10 +5694,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>-466.8415345</t>
-        </is>
+      <c r="D58" t="n">
+        <v>-466.8415345</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -5838,10 +5724,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>-473.5213852</t>
-        </is>
+      <c r="D59" t="n">
+        <v>-473.5213852</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -5870,10 +5754,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>-481.2656462</t>
-        </is>
+      <c r="D60" t="n">
+        <v>-481.2656462</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -5902,10 +5784,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>-490.913796</t>
-        </is>
+      <c r="D61" t="n">
+        <v>-490.913796</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -5934,10 +5814,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>54.04706315</t>
-        </is>
+      <c r="D62" t="n">
+        <v>54.04706315</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -5966,10 +5844,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>52.58377128</t>
-        </is>
+      <c r="D63" t="n">
+        <v>52.58377128</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -5998,10 +5874,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>53.24037925</t>
-        </is>
+      <c r="D64" t="n">
+        <v>53.24037925</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -6030,10 +5904,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>56.13877316</t>
-        </is>
+      <c r="D65" t="n">
+        <v>56.13877316</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -6062,10 +5934,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>59.80754068</t>
-        </is>
+      <c r="D66" t="n">
+        <v>59.80754068</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -6094,10 +5964,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>63.30020599</t>
-        </is>
+      <c r="D67" t="n">
+        <v>63.30020599</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -6126,10 +5994,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>66.45033347</t>
-        </is>
+      <c r="D68" t="n">
+        <v>66.45033347</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -6158,10 +6024,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>68.7357972</t>
-        </is>
+      <c r="D69" t="n">
+        <v>68.73579719999999</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -6190,10 +6054,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>69.10338285</t>
-        </is>
+      <c r="D70" t="n">
+        <v>69.10338285</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -6222,10 +6084,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>67.470239</t>
-        </is>
+      <c r="D71" t="n">
+        <v>67.47023900000001</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -6254,10 +6114,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>64.94029275</t>
-        </is>
+      <c r="D72" t="n">
+        <v>64.94029275</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -6286,10 +6144,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>62.88001818</t>
-        </is>
+      <c r="D73" t="n">
+        <v>62.88001818</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -6318,10 +6174,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>61.86704806</t>
-        </is>
+      <c r="D74" t="n">
+        <v>61.86704806</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -6350,10 +6204,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>61.43487765</t>
-        </is>
+      <c r="D75" t="n">
+        <v>61.43487765</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -6382,10 +6234,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>61.24283233</t>
-        </is>
+      <c r="D76" t="n">
+        <v>61.24283233</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -6414,10 +6264,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>61.9885188</t>
-        </is>
+      <c r="D77" t="n">
+        <v>61.9885188</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -6446,10 +6294,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>62.84407169</t>
-        </is>
+      <c r="D78" t="n">
+        <v>62.84407169</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -6478,10 +6324,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>63.88504573</t>
-        </is>
+      <c r="D79" t="n">
+        <v>63.88504573</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -6510,10 +6354,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>64.98221081</t>
-        </is>
+      <c r="D80" t="n">
+        <v>64.98221081</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -6542,10 +6384,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>66.14383658</t>
-        </is>
+      <c r="D81" t="n">
+        <v>66.14383658</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -6574,10 +6414,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>75.9406371</t>
-        </is>
+      <c r="D82" t="n">
+        <v>75.9406371</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -6606,10 +6444,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>76.20612508</t>
-        </is>
+      <c r="D83" t="n">
+        <v>76.20612508000001</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -6638,10 +6474,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>77.92553661</t>
-        </is>
+      <c r="D84" t="n">
+        <v>77.92553660999999</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -6670,10 +6504,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>80.66842827</t>
-        </is>
+      <c r="D85" t="n">
+        <v>80.66842827000001</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -6702,10 +6534,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>81.85242805</t>
-        </is>
+      <c r="D86" t="n">
+        <v>81.85242805</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -6734,10 +6564,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>79.4740621</t>
-        </is>
+      <c r="D87" t="n">
+        <v>79.4740621</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -6766,10 +6594,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>75.33004228</t>
-        </is>
+      <c r="D88" t="n">
+        <v>75.33004228</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -6798,10 +6624,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>70.91104353</t>
-        </is>
+      <c r="D89" t="n">
+        <v>70.91104353</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -6830,10 +6654,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>67.24495457</t>
-        </is>
+      <c r="D90" t="n">
+        <v>67.24495457</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -6862,10 +6684,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>64.18892654</t>
-        </is>
+      <c r="D91" t="n">
+        <v>64.18892654</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -6894,10 +6714,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>61.94036885</t>
-        </is>
+      <c r="D92" t="n">
+        <v>61.94036885</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -6926,10 +6744,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>61.28406345</t>
-        </is>
+      <c r="D93" t="n">
+        <v>61.28406345</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -6958,10 +6774,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>62.02625725</t>
-        </is>
+      <c r="D94" t="n">
+        <v>62.02625725</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -6990,10 +6804,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>64.28970117</t>
-        </is>
+      <c r="D95" t="n">
+        <v>64.28970117</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -7022,10 +6834,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>66.6648914</t>
-        </is>
+      <c r="D96" t="n">
+        <v>66.6648914</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -7054,10 +6864,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>67.58677375</t>
-        </is>
+      <c r="D97" t="n">
+        <v>67.58677375000001</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -7086,10 +6894,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>68.33510534</t>
-        </is>
+      <c r="D98" t="n">
+        <v>68.33510534</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -7118,10 +6924,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>68.92169056</t>
-        </is>
+      <c r="D99" t="n">
+        <v>68.92169056</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -7150,10 +6954,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>69.30681282</t>
-        </is>
+      <c r="D100" t="n">
+        <v>69.30681282</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -7182,10 +6984,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>69.52709972</t>
-        </is>
+      <c r="D101" t="n">
+        <v>69.52709972</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -7214,10 +7014,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>438.7831324</t>
-        </is>
+      <c r="D102" t="n">
+        <v>438.7831324</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -7246,10 +7044,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>444.4235622</t>
-        </is>
+      <c r="D103" t="n">
+        <v>444.4235622</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -7278,10 +7074,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>450.2340837</t>
-        </is>
+      <c r="D104" t="n">
+        <v>450.2340837</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -7310,10 +7104,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>456.3173784</t>
-        </is>
+      <c r="D105" t="n">
+        <v>456.3173784</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -7342,10 +7134,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>462.8149366</t>
-        </is>
+      <c r="D106" t="n">
+        <v>462.8149366</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -7374,10 +7164,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>466.6107322</t>
-        </is>
+      <c r="D107" t="n">
+        <v>466.6107322</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -7406,10 +7194,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>466.4578043</t>
-        </is>
+      <c r="D108" t="n">
+        <v>466.4578043</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -7438,10 +7224,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>462.5210038</t>
-        </is>
+      <c r="D109" t="n">
+        <v>462.5210038</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -7470,10 +7254,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>454.3540696</t>
-        </is>
+      <c r="D110" t="n">
+        <v>454.3540696</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -7502,10 +7284,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>445.2111756</t>
-        </is>
+      <c r="D111" t="n">
+        <v>445.2111756</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -7534,10 +7314,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>437.7889326</t>
-        </is>
+      <c r="D112" t="n">
+        <v>437.7889326</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -7566,10 +7344,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>433.9366219</t>
-        </is>
+      <c r="D113" t="n">
+        <v>433.9366219</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -7598,10 +7374,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>431.8648179</t>
-        </is>
+      <c r="D114" t="n">
+        <v>431.8648179</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -7630,10 +7404,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>430.5842136</t>
-        </is>
+      <c r="D115" t="n">
+        <v>430.5842136</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -7662,10 +7434,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>432.0113103</t>
-        </is>
+      <c r="D116" t="n">
+        <v>432.0113103</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -7694,10 +7464,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>440.6923497</t>
-        </is>
+      <c r="D117" t="n">
+        <v>440.6923497</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -7726,10 +7494,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>449.661918</t>
-        </is>
+      <c r="D118" t="n">
+        <v>449.661918</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -7758,10 +7524,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>459.2365397</t>
-        </is>
+      <c r="D119" t="n">
+        <v>459.2365397</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -7790,10 +7554,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>468.6884586</t>
-        </is>
+      <c r="D120" t="n">
+        <v>468.6884586</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -7822,10 +7584,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>478.6451452</t>
-        </is>
+      <c r="D121" t="n">
+        <v>478.6451452</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -7854,10 +7614,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>1.238320455</t>
-        </is>
+      <c r="D122" t="n">
+        <v>1.238320455</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -7886,10 +7644,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>1.216598924</t>
-        </is>
+      <c r="D123" t="n">
+        <v>1.216598924</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -7918,10 +7674,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>1.249965438</t>
-        </is>
+      <c r="D124" t="n">
+        <v>1.249965438</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -7950,10 +7704,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>1.22879138</t>
-        </is>
+      <c r="D125" t="n">
+        <v>1.22879138</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -7982,10 +7734,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>1.18583506</t>
-        </is>
+      <c r="D126" t="n">
+        <v>1.18583506</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -8014,10 +7764,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>1.230704286</t>
-        </is>
+      <c r="D127" t="n">
+        <v>1.230704286</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -8046,10 +7794,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>1.243853596</t>
-        </is>
+      <c r="D128" t="n">
+        <v>1.243853596</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -8078,10 +7824,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>1.232930275</t>
-        </is>
+      <c r="D129" t="n">
+        <v>1.232930275</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -8110,10 +7854,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>1.232634692</t>
-        </is>
+      <c r="D130" t="n">
+        <v>1.232634692</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -8142,10 +7884,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>1.241933893</t>
-        </is>
+      <c r="D131" t="n">
+        <v>1.241933893</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -8174,10 +7914,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>1.259142128</t>
-        </is>
+      <c r="D132" t="n">
+        <v>1.259142128</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -8206,10 +7944,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>1.188242134</t>
-        </is>
+      <c r="D133" t="n">
+        <v>1.188242134</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -8238,10 +7974,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>1.183804514</t>
-        </is>
+      <c r="D134" t="n">
+        <v>1.183804514</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -8270,10 +8004,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>1.182419769</t>
-        </is>
+      <c r="D135" t="n">
+        <v>1.182419769</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -8302,10 +8034,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>1.184460933</t>
-        </is>
+      <c r="D136" t="n">
+        <v>1.184460933</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -8334,10 +8064,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>1.195575082</t>
-        </is>
+      <c r="D137" t="n">
+        <v>1.195575082</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -8366,10 +8094,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>1.176568921</t>
-        </is>
+      <c r="D138" t="n">
+        <v>1.176568921</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -8398,10 +8124,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>1.207861855</t>
-        </is>
+      <c r="D139" t="n">
+        <v>1.207861855</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -8430,10 +8154,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>1.196378645</t>
-        </is>
+      <c r="D140" t="n">
+        <v>1.196378645</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -8462,10 +8184,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>1.202213453</t>
-        </is>
+      <c r="D141" t="n">
+        <v>1.202213453</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -8494,10 +8214,8 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>1.206417703</t>
-        </is>
+      <c r="D142" t="n">
+        <v>1.206417703</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -8526,10 +8244,8 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>1.209469472</t>
-        </is>
+      <c r="D143" t="n">
+        <v>1.209469472</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -8558,10 +8274,8 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>1.200284646</t>
-        </is>
+      <c r="D144" t="n">
+        <v>1.200284646</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -8590,10 +8304,8 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>1.19441061</t>
-        </is>
+      <c r="D145" t="n">
+        <v>1.19441061</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -8622,10 +8334,8 @@
           <t>2027-01</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>1.181769365</t>
-        </is>
+      <c r="D146" t="n">
+        <v>1.181769365</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -8654,10 +8364,8 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>1.188769365</t>
-        </is>
+      <c r="D147" t="n">
+        <v>1.188769365</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -8686,10 +8394,8 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>1.195808564</t>
-        </is>
+      <c r="D148" t="n">
+        <v>1.195808564</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -8718,10 +8424,8 @@
           <t>2027-04</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>1.199358441</t>
-        </is>
+      <c r="D149" t="n">
+        <v>1.199358441</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -8750,10 +8454,8 @@
           <t>2027-05</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>1.202729804</t>
-        </is>
+      <c r="D150" t="n">
+        <v>1.202729804</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -8782,10 +8484,8 @@
           <t>2027-06</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>1.206126332</t>
-        </is>
+      <c r="D151" t="n">
+        <v>1.206126332</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -8814,10 +8514,8 @@
           <t>2027-07</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>1.21016884</t>
-        </is>
+      <c r="D152" t="n">
+        <v>1.21016884</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -8846,10 +8544,8 @@
           <t>2027-08</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>1.214745678</t>
-        </is>
+      <c r="D153" t="n">
+        <v>1.214745678</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -8878,10 +8574,8 @@
           <t>2027-09</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>1.218783997</t>
-        </is>
+      <c r="D154" t="n">
+        <v>1.218783997</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -8910,10 +8604,8 @@
           <t>2027-10</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>1.221758194</t>
-        </is>
+      <c r="D155" t="n">
+        <v>1.221758194</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -8942,10 +8634,8 @@
           <t>2027-11</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>1.224637876</t>
-        </is>
+      <c r="D156" t="n">
+        <v>1.224637876</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -8974,10 +8664,8 @@
           <t>2027-12</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>1.22690578</t>
-        </is>
+      <c r="D157" t="n">
+        <v>1.22690578</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -9006,10 +8694,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1.107449676</t>
-        </is>
+      <c r="D158" t="n">
+        <v>1.107449676</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -9038,10 +8724,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>1.169087803</t>
-        </is>
+      <c r="D159" t="n">
+        <v>1.169087803</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -9070,10 +8754,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>1.181333344</t>
-        </is>
+      <c r="D160" t="n">
+        <v>1.181333344</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -9102,10 +8784,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>1.197795</t>
-        </is>
+      <c r="D161" t="n">
+        <v>1.197795</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -9134,10 +8814,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>1.193542074</t>
-        </is>
+      <c r="D162" t="n">
+        <v>1.193542074</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -9166,10 +8844,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>1.191418703</t>
-        </is>
+      <c r="D163" t="n">
+        <v>1.191418703</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -9198,10 +8874,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>1.205998983</t>
-        </is>
+      <c r="D164" t="n">
+        <v>1.205998983</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -9230,10 +8904,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>1.187634285</t>
-        </is>
+      <c r="D165" t="n">
+        <v>1.187634285</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -9262,10 +8934,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>1.147020332</t>
-        </is>
+      <c r="D166" t="n">
+        <v>1.147020332</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -9294,10 +8964,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>1.106165401</t>
-        </is>
+      <c r="D167" t="n">
+        <v>1.106165401</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -9326,10 +8994,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>1.137</t>
-        </is>
+      <c r="D168" t="n">
+        <v>1.137</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -9358,10 +9024,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>1.133</t>
-        </is>
+      <c r="D169" t="n">
+        <v>1.133</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -9390,10 +9054,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>1.127</t>
-        </is>
+      <c r="D170" t="n">
+        <v>1.127</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -9422,10 +9084,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>1.138</t>
-        </is>
+      <c r="D171" t="n">
+        <v>1.138</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -9454,10 +9114,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>1.143829693</t>
-        </is>
+      <c r="D172" t="n">
+        <v>1.143829693</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -9486,10 +9144,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>1.15585008</t>
-        </is>
+      <c r="D173" t="n">
+        <v>1.15585008</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -9518,10 +9174,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>1.14635167</t>
-        </is>
+      <c r="D174" t="n">
+        <v>1.14635167</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -9550,10 +9204,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>1.131632615</t>
-        </is>
+      <c r="D175" t="n">
+        <v>1.131632615</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -9582,10 +9234,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>1.144854077</t>
-        </is>
+      <c r="D176" t="n">
+        <v>1.144854077</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -9614,10 +9264,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>1.147220762</t>
-        </is>
+      <c r="D177" t="n">
+        <v>1.147220762</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -9646,10 +9294,8 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>1.152855494</t>
-        </is>
+      <c r="D178" t="n">
+        <v>1.152855494</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -9678,10 +9324,8 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>1.158720159</t>
-        </is>
+      <c r="D179" t="n">
+        <v>1.158720159</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -9710,10 +9354,8 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>1.166765248</t>
-        </is>
+      <c r="D180" t="n">
+        <v>1.166765248</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -9742,10 +9384,8 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>1.176581454</t>
-        </is>
+      <c r="D181" t="n">
+        <v>1.176581454</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -9774,10 +9414,8 @@
           <t>2027-01</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>1.181965328</t>
-        </is>
+      <c r="D182" t="n">
+        <v>1.181965328</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -9806,10 +9444,8 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>1.189965328</t>
-        </is>
+      <c r="D183" t="n">
+        <v>1.189965328</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -9838,10 +9474,8 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>1.195138433</t>
-        </is>
+      <c r="D184" t="n">
+        <v>1.195138433</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -9870,10 +9504,8 @@
           <t>2027-04</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>1.201117877</t>
-        </is>
+      <c r="D185" t="n">
+        <v>1.201117877</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -9902,10 +9534,8 @@
           <t>2027-05</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>1.206600158</t>
-        </is>
+      <c r="D186" t="n">
+        <v>1.206600158</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -9934,10 +9564,8 @@
           <t>2027-06</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>1.21165409</t>
-        </is>
+      <c r="D187" t="n">
+        <v>1.21165409</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -9966,10 +9594,8 @@
           <t>2027-07</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>1.215958912</t>
-        </is>
+      <c r="D188" t="n">
+        <v>1.215958912</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -9998,10 +9624,8 @@
           <t>2027-08</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>1.219194374</t>
-        </is>
+      <c r="D189" t="n">
+        <v>1.219194374</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -10030,10 +9654,8 @@
           <t>2027-09</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>1.221864555</t>
-        </is>
+      <c r="D190" t="n">
+        <v>1.221864555</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -10062,10 +9684,8 @@
           <t>2027-10</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>1.224107372</t>
-        </is>
+      <c r="D191" t="n">
+        <v>1.224107372</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -10094,10 +9714,8 @@
           <t>2027-11</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr">
-        <is>
-          <t>1.225236354</t>
-        </is>
+      <c r="D192" t="n">
+        <v>1.225236354</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -10126,10 +9744,8 @@
           <t>2027-12</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>1.225003002</t>
-        </is>
+      <c r="D193" t="n">
+        <v>1.225003002</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -10158,10 +9774,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>6.267037895</t>
-        </is>
+      <c r="D194" t="n">
+        <v>6.267037895</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -10190,10 +9804,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr">
-        <is>
-          <t>6.356523699</t>
-        </is>
+      <c r="D195" t="n">
+        <v>6.356523699</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -10222,10 +9834,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>6.495038972</t>
-        </is>
+      <c r="D196" t="n">
+        <v>6.495038972</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -10254,10 +9864,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>6.513277699</t>
-        </is>
+      <c r="D197" t="n">
+        <v>6.513277699</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -10286,10 +9894,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>6.507772496</t>
-        </is>
+      <c r="D198" t="n">
+        <v>6.507772496</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -10318,10 +9924,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>6.515732331</t>
-        </is>
+      <c r="D199" t="n">
+        <v>6.515732331</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -10350,10 +9954,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>6.642495456</t>
-        </is>
+      <c r="D200" t="n">
+        <v>6.642495456</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -10382,10 +9984,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>6.66541779</t>
-        </is>
+      <c r="D201" t="n">
+        <v>6.66541779</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -10414,10 +10014,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>6.714492408</t>
-        </is>
+      <c r="D202" t="n">
+        <v>6.714492408</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -10446,10 +10044,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>6.750376811</t>
-        </is>
+      <c r="D203" t="n">
+        <v>6.750376811</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -10478,10 +10074,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>6.760062212</t>
-        </is>
+      <c r="D204" t="n">
+        <v>6.760062212</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -10510,10 +10104,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>6.67140531</t>
-        </is>
+      <c r="D205" t="n">
+        <v>6.67140531</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -10542,10 +10134,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>6.362111001</t>
-        </is>
+      <c r="D206" t="n">
+        <v>6.362111001</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -10574,10 +10164,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>6.74858646</t>
-        </is>
+      <c r="D207" t="n">
+        <v>6.74858646</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -10606,10 +10194,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>6.718287604</t>
-        </is>
+      <c r="D208" t="n">
+        <v>6.718287604</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -10638,10 +10224,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>6.819432393</t>
-        </is>
+      <c r="D209" t="n">
+        <v>6.819432393</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -10670,10 +10254,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>6.823423755</t>
-        </is>
+      <c r="D210" t="n">
+        <v>6.823423755</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -10702,10 +10284,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>6.735286088</t>
-        </is>
+      <c r="D211" t="n">
+        <v>6.735286088</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -10734,10 +10314,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>6.75337689</t>
-        </is>
+      <c r="D212" t="n">
+        <v>6.75337689</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -10766,10 +10344,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>6.79001279</t>
-        </is>
+      <c r="D213" t="n">
+        <v>6.79001279</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -10798,10 +10374,8 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>6.834065554</t>
-        </is>
+      <c r="D214" t="n">
+        <v>6.834065554</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -10830,10 +10404,8 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>6.84341534</t>
-        </is>
+      <c r="D215" t="n">
+        <v>6.84341534</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -10862,10 +10434,8 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>6.868104866</t>
-        </is>
+      <c r="D216" t="n">
+        <v>6.868104866</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -10894,10 +10464,8 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>6.887998863</t>
-        </is>
+      <c r="D217" t="n">
+        <v>6.887998863</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -10926,10 +10494,8 @@
           <t>2027-01</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>6.869544268</t>
-        </is>
+      <c r="D218" t="n">
+        <v>6.869544268</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -10958,10 +10524,8 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>6.95544268</t>
-        </is>
+      <c r="D219" t="n">
+        <v>6.95544268</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -10990,10 +10554,8 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>7.00091871</t>
-        </is>
+      <c r="D220" t="n">
+        <v>7.00091871</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -11022,10 +10584,8 @@
           <t>2027-04</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>7.03583526</t>
-        </is>
+      <c r="D221" t="n">
+        <v>7.03583526</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -11054,10 +10614,8 @@
           <t>2027-05</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>7.070569161</t>
-        </is>
+      <c r="D222" t="n">
+        <v>7.070569161</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -11086,10 +10644,8 @@
           <t>2027-06</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>7.103520228</t>
-        </is>
+      <c r="D223" t="n">
+        <v>7.103520228</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -11118,10 +10674,8 @@
           <t>2027-07</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>7.134023137</t>
-        </is>
+      <c r="D224" t="n">
+        <v>7.134023137</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -11150,10 +10704,8 @@
           <t>2027-08</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>7.161545921</t>
-        </is>
+      <c r="D225" t="n">
+        <v>7.161545921</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -11182,10 +10734,8 @@
           <t>2027-09</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>7.186272942</t>
-        </is>
+      <c r="D226" t="n">
+        <v>7.186272942</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -11214,10 +10764,8 @@
           <t>2027-10</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>7.207899359</t>
-        </is>
+      <c r="D227" t="n">
+        <v>7.207899359</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -11246,10 +10794,8 @@
           <t>2027-11</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>7.224091995</t>
-        </is>
+      <c r="D228" t="n">
+        <v>7.224091995</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -11278,10 +10824,8 @@
           <t>2027-12</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>7.235838597</t>
-        </is>
+      <c r="D229" t="n">
+        <v>7.235838597</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -11310,10 +10854,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>2.100925588</t>
-        </is>
+      <c r="D230" t="n">
+        <v>2.100925588</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -11342,10 +10884,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>2.104028222</t>
-        </is>
+      <c r="D231" t="n">
+        <v>2.104028222</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -11374,10 +10914,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>2.146079646</t>
-        </is>
+      <c r="D232" t="n">
+        <v>2.146079646</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -11406,10 +10944,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>2.134423295</t>
-        </is>
+      <c r="D233" t="n">
+        <v>2.134423295</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -11438,10 +10974,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr">
-        <is>
-          <t>2.14459247</t>
-        </is>
+      <c r="D234" t="n">
+        <v>2.14459247</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -11470,10 +11004,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr">
-        <is>
-          <t>2.133601282</t>
-        </is>
+      <c r="D235" t="n">
+        <v>2.133601282</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -11502,10 +11034,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>2.115039397</t>
-        </is>
+      <c r="D236" t="n">
+        <v>2.115039397</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -11534,10 +11064,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>2.102938156</t>
-        </is>
+      <c r="D237" t="n">
+        <v>2.102938156</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -11566,10 +11094,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>2.111183215</t>
-        </is>
+      <c r="D238" t="n">
+        <v>2.111183215</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -11598,10 +11124,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr">
-        <is>
-          <t>2.106149357</t>
-        </is>
+      <c r="D239" t="n">
+        <v>2.106149357</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -11630,10 +11154,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr">
-        <is>
-          <t>2.059945</t>
-        </is>
+      <c r="D240" t="n">
+        <v>2.059945</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -11662,10 +11184,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>2.069296177</t>
-        </is>
+      <c r="D241" t="n">
+        <v>2.069296177</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -11694,10 +11214,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>1.93498244</t>
-        </is>
+      <c r="D242" t="n">
+        <v>1.93498244</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -11726,10 +11244,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>2.015148931</t>
-        </is>
+      <c r="D243" t="n">
+        <v>2.015148931</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -11758,10 +11274,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>2.044020023</t>
-        </is>
+      <c r="D244" t="n">
+        <v>2.044020023</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -11790,10 +11304,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>2.038198542</t>
-        </is>
+      <c r="D245" t="n">
+        <v>2.038198542</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -11822,10 +11334,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>2.053961293</t>
-        </is>
+      <c r="D246" t="n">
+        <v>2.053961293</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -11854,10 +11364,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>2.064534225</t>
-        </is>
+      <c r="D247" t="n">
+        <v>2.064534225</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -11886,10 +11394,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>2.051606963</t>
-        </is>
+      <c r="D248" t="n">
+        <v>2.051606963</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -11918,10 +11424,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>2.051983053</t>
-        </is>
+      <c r="D249" t="n">
+        <v>2.051983053</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -11950,10 +11454,8 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>2.053792004</t>
-        </is>
+      <c r="D250" t="n">
+        <v>2.053792004</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -11982,10 +11484,8 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>2.049007319</t>
-        </is>
+      <c r="D251" t="n">
+        <v>2.049007319</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -12014,10 +11514,8 @@
           <t>2026-11</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>2.049220391</t>
-        </is>
+      <c r="D252" t="n">
+        <v>2.049220391</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -12046,10 +11544,8 @@
           <t>2026-12</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>2.060530929</t>
-        </is>
+      <c r="D253" t="n">
+        <v>2.060530929</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -12078,10 +11574,8 @@
           <t>2027-01</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>2.057326755</t>
-        </is>
+      <c r="D254" t="n">
+        <v>2.057326755</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -12110,10 +11604,8 @@
           <t>2027-02</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>2.06993581</t>
-        </is>
+      <c r="D255" t="n">
+        <v>2.06993581</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -12142,10 +11634,8 @@
           <t>2027-03</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>2.082114472</t>
-        </is>
+      <c r="D256" t="n">
+        <v>2.082114472</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -12174,10 +11664,8 @@
           <t>2027-04</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>2.094164006</t>
-        </is>
+      <c r="D257" t="n">
+        <v>2.094164006</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -12206,10 +11694,8 @@
           <t>2027-05</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>2.10596423</t>
-        </is>
+      <c r="D258" t="n">
+        <v>2.10596423</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -12238,10 +11724,8 @@
           <t>2027-06</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>2.116659087</t>
-        </is>
+      <c r="D259" t="n">
+        <v>2.116659087</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -12270,10 +11754,8 @@
           <t>2027-07</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr">
-        <is>
-          <t>2.126379596</t>
-        </is>
+      <c r="D260" t="n">
+        <v>2.126379596</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -12302,10 +11784,8 @@
           <t>2027-08</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>2.135590934</t>
-        </is>
+      <c r="D261" t="n">
+        <v>2.135590934</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -12334,10 +11814,8 @@
           <t>2027-09</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>2.144140539</t>
-        </is>
+      <c r="D262" t="n">
+        <v>2.144140539</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -12366,10 +11844,8 @@
           <t>2027-10</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr">
-        <is>
-          <t>2.150780121</t>
-        </is>
+      <c r="D263" t="n">
+        <v>2.150780121</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -12398,10 +11874,8 @@
           <t>2027-11</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>2.155350812</t>
-        </is>
+      <c r="D264" t="n">
+        <v>2.155350812</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -12430,10 +11904,8 @@
           <t>2027-12</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>2.15894052</t>
-        </is>
+      <c r="D265" t="n">
+        <v>2.15894052</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -12462,10 +11934,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
+      <c r="D266" t="n">
+        <v>40</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -12489,10 +11959,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
+      <c r="D267" t="n">
+        <v>37</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -12516,10 +11984,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="D268" t="n">
+        <v>69</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -12543,10 +12009,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
+      <c r="D269" t="n">
+        <v>83</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -12570,10 +12034,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
+      <c r="D270" t="n">
+        <v>73</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -12597,10 +12059,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
+      <c r="D271" t="n">
+        <v>84</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -12624,10 +12084,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
+      <c r="D272" t="n">
+        <v>72</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -12651,10 +12109,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="D273" t="n">
+        <v>67</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -12678,10 +12134,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="D274" t="n">
+        <v>80</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -12705,10 +12159,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="D275" t="n">
+        <v>75</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -12732,10 +12184,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
+      <c r="D276" t="n">
+        <v>63</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -12759,10 +12209,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
+      <c r="D277" t="n">
+        <v>62</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -12786,10 +12234,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="D278" t="n">
+        <v>55</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -12813,10 +12259,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
+      <c r="D279" t="n">
+        <v>58</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -12840,10 +12284,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="D280" t="n">
+        <v>75</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -12867,10 +12309,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="D281" t="n">
+        <v>80</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -12894,10 +12334,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
+      <c r="D282" t="n">
+        <v>70</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -12921,10 +12359,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
+      <c r="D283" t="n">
+        <v>75</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -12948,10 +12384,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="D284" t="n">
+        <v>69</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -12975,10 +12409,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="D285" t="n">
+        <v>69</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -13002,10 +12434,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
+      <c r="D286" t="n">
+        <v>129</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -13029,10 +12459,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+      <c r="D287" t="n">
+        <v>101</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -13056,10 +12484,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
+      <c r="D288" t="n">
+        <v>139</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -13083,10 +12509,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
+      <c r="D289" t="n">
+        <v>126</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -13110,10 +12534,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
+      <c r="D290" t="n">
+        <v>123</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
@@ -13137,10 +12559,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
+      <c r="D291" t="n">
+        <v>112</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
@@ -13164,10 +12584,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="D292" t="n">
+        <v>100</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
@@ -13191,10 +12609,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
+      <c r="D293" t="n">
+        <v>69</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
@@ -13218,10 +12634,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="D294" t="n">
+        <v>105</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
@@ -13245,10 +12659,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="D295" t="n">
+        <v>100</v>
       </c>
       <c r="E295" t="inlineStr">
         <is>
@@ -13272,10 +12684,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+      <c r="D296" t="n">
+        <v>86</v>
       </c>
       <c r="E296" t="inlineStr">
         <is>
@@ -13299,10 +12709,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
+      <c r="D297" t="n">
+        <v>95</v>
       </c>
       <c r="E297" t="inlineStr">
         <is>
@@ -13326,10 +12734,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
+      <c r="D298" t="n">
+        <v>100</v>
       </c>
       <c r="E298" t="inlineStr">
         <is>
@@ -13353,10 +12759,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="D299" t="n">
+        <v>105</v>
       </c>
       <c r="E299" t="inlineStr">
         <is>
@@ -13380,10 +12784,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
+      <c r="D300" t="n">
+        <v>105</v>
       </c>
       <c r="E300" t="inlineStr">
         <is>
@@ -13407,10 +12809,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+      <c r="D301" t="n">
+        <v>98</v>
       </c>
       <c r="E301" t="inlineStr">
         <is>
@@ -13434,10 +12834,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="D302" t="n">
+        <v>117</v>
       </c>
       <c r="E302" t="inlineStr">
         <is>
@@ -13461,10 +12859,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
+      <c r="D303" t="n">
+        <v>111</v>
       </c>
       <c r="E303" t="inlineStr">
         <is>
@@ -13488,10 +12884,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
+      <c r="D304" t="n">
+        <v>117</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
@@ -13515,10 +12909,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
+      <c r="D305" t="n">
+        <v>118</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
@@ -13542,10 +12934,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>527</t>
-        </is>
+      <c r="D306" t="n">
+        <v>527</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
@@ -13569,10 +12959,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
+      <c r="D307" t="n">
+        <v>524</v>
       </c>
       <c r="E307" t="inlineStr">
         <is>
@@ -13596,10 +12984,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr">
-        <is>
-          <t>506</t>
-        </is>
+      <c r="D308" t="n">
+        <v>506</v>
       </c>
       <c r="E308" t="inlineStr">
         <is>
@@ -13623,10 +13009,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
+      <c r="D309" t="n">
+        <v>579</v>
       </c>
       <c r="E309" t="inlineStr">
         <is>
@@ -13650,10 +13034,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
+      <c r="D310" t="n">
+        <v>492</v>
       </c>
       <c r="E310" t="inlineStr">
         <is>
@@ -13677,10 +13059,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr">
-        <is>
-          <t>457</t>
-        </is>
+      <c r="D311" t="n">
+        <v>457</v>
       </c>
       <c r="E311" t="inlineStr">
         <is>
@@ -13704,10 +13084,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
+      <c r="D312" t="n">
+        <v>421</v>
       </c>
       <c r="E312" t="inlineStr">
         <is>
@@ -13731,10 +13109,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
+      <c r="D313" t="n">
+        <v>542</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
@@ -13758,10 +13134,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
+      <c r="D314" t="n">
+        <v>487</v>
       </c>
       <c r="E314" t="inlineStr">
         <is>
@@ -13785,10 +13159,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>470</t>
-        </is>
+      <c r="D315" t="n">
+        <v>470</v>
       </c>
       <c r="E315" t="inlineStr">
         <is>
@@ -13812,10 +13184,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
+      <c r="D316" t="n">
+        <v>525</v>
       </c>
       <c r="E316" t="inlineStr">
         <is>
@@ -13839,10 +13209,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>467</t>
-        </is>
+      <c r="D317" t="n">
+        <v>467</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
@@ -13866,10 +13234,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
+      <c r="D318" t="n">
+        <v>432</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
@@ -13893,10 +13259,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr">
-        <is>
-          <t>451</t>
-        </is>
+      <c r="D319" t="n">
+        <v>451</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
@@ -13920,10 +13284,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>452</t>
-        </is>
+      <c r="D320" t="n">
+        <v>452</v>
       </c>
       <c r="E320" t="inlineStr">
         <is>
@@ -13947,10 +13309,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
+      <c r="D321" t="n">
+        <v>475</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
@@ -13974,10 +13334,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>462</t>
-        </is>
+      <c r="D322" t="n">
+        <v>462</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
@@ -14001,10 +13359,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
+      <c r="D323" t="n">
+        <v>475</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
@@ -14028,10 +13384,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>484</t>
-        </is>
+      <c r="D324" t="n">
+        <v>484</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
@@ -14055,10 +13409,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>488</t>
-        </is>
+      <c r="D325" t="n">
+        <v>488</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
@@ -14082,10 +13434,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
+      <c r="D326" t="n">
+        <v>34.8</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
@@ -14109,10 +13459,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>33.25</t>
-        </is>
+      <c r="D327" t="n">
+        <v>33.25</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
@@ -14136,10 +13484,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>33.25</t>
-        </is>
+      <c r="D328" t="n">
+        <v>33.25</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
@@ -14163,10 +13509,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
+      <c r="D329" t="n">
+        <v>33</v>
       </c>
       <c r="E329" t="inlineStr">
         <is>
@@ -14190,10 +13534,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>32.2</t>
-        </is>
+      <c r="D330" t="n">
+        <v>32.2</v>
       </c>
       <c r="E330" t="inlineStr">
         <is>
@@ -14217,10 +13559,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="D331" t="n">
+        <v>31</v>
       </c>
       <c r="E331" t="inlineStr">
         <is>
@@ -14244,10 +13584,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="D332" t="n">
+        <v>31</v>
       </c>
       <c r="E332" t="inlineStr">
         <is>
@@ -14271,10 +13609,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>30.4</t>
-        </is>
+      <c r="D333" t="n">
+        <v>30.4</v>
       </c>
       <c r="E333" t="inlineStr">
         <is>
@@ -14298,10 +13634,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="D334" t="n">
+        <v>29</v>
       </c>
       <c r="E334" t="inlineStr">
         <is>
@@ -14325,10 +13659,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>29.8</t>
-        </is>
+      <c r="D335" t="n">
+        <v>29.8</v>
       </c>
       <c r="E335" t="inlineStr">
         <is>
@@ -14352,10 +13684,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>29.25</t>
-        </is>
+      <c r="D336" t="n">
+        <v>29.25</v>
       </c>
       <c r="E336" t="inlineStr">
         <is>
@@ -14379,10 +13709,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="D337" t="n">
+        <v>29</v>
       </c>
       <c r="E337" t="inlineStr">
         <is>
@@ -14406,10 +13734,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>28.4</t>
-        </is>
+      <c r="D338" t="n">
+        <v>28.4</v>
       </c>
       <c r="E338" t="inlineStr">
         <is>
@@ -14433,10 +13759,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>28.25</t>
-        </is>
+      <c r="D339" t="n">
+        <v>28.25</v>
       </c>
       <c r="E339" t="inlineStr">
         <is>
@@ -14460,10 +13784,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="D340" t="n">
+        <v>28</v>
       </c>
       <c r="E340" t="inlineStr">
         <is>
@@ -14487,10 +13809,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>28.25</t>
-        </is>
+      <c r="D341" t="n">
+        <v>28.25</v>
       </c>
       <c r="E341" t="inlineStr">
         <is>
@@ -14514,10 +13834,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="D342" t="n">
+        <v>28</v>
       </c>
       <c r="E342" t="inlineStr">
         <is>
@@ -14541,10 +13859,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="D343" t="n">
+        <v>28</v>
       </c>
       <c r="E343" t="inlineStr">
         <is>
@@ -14568,10 +13884,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="D344" t="n">
+        <v>27</v>
       </c>
       <c r="E344" t="inlineStr">
         <is>
@@ -14595,10 +13909,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="D345" t="n">
+        <v>27</v>
       </c>
       <c r="E345" t="inlineStr">
         <is>
@@ -14622,10 +13934,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
+      <c r="D346" t="n">
+        <v>49.4</v>
       </c>
       <c r="E346" t="inlineStr">
         <is>
@@ -14649,10 +13959,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
+      <c r="D347" t="n">
+        <v>52.5</v>
       </c>
       <c r="E347" t="inlineStr">
         <is>
@@ -14676,10 +13984,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
+      <c r="D348" t="n">
+        <v>53</v>
       </c>
       <c r="E348" t="inlineStr">
         <is>
@@ -14703,10 +14009,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>52.75</t>
-        </is>
+      <c r="D349" t="n">
+        <v>52.75</v>
       </c>
       <c r="E349" t="inlineStr">
         <is>
@@ -14730,10 +14034,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>51.4</t>
-        </is>
+      <c r="D350" t="n">
+        <v>51.4</v>
       </c>
       <c r="E350" t="inlineStr">
         <is>
@@ -14757,10 +14059,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="D351" t="n">
+        <v>49</v>
       </c>
       <c r="E351" t="inlineStr">
         <is>
@@ -14784,10 +14084,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
+      <c r="D352" t="n">
+        <v>49.5</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
@@ -14811,10 +14109,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
+      <c r="D353" t="n">
+        <v>48.8</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
@@ -14838,10 +14134,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
+      <c r="D354" t="n">
+        <v>51.5</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
@@ -14865,10 +14159,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>54.4</t>
-        </is>
+      <c r="D355" t="n">
+        <v>54.4</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
@@ -14892,10 +14184,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="D356" t="n">
+        <v>51</v>
       </c>
       <c r="E356" t="inlineStr">
         <is>
@@ -14919,10 +14209,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
+      <c r="D357" t="n">
+        <v>49</v>
       </c>
       <c r="E357" t="inlineStr">
         <is>
@@ -14946,10 +14234,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="D358" t="n">
+        <v>47.4</v>
       </c>
       <c r="E358" t="inlineStr">
         <is>
@@ -14973,10 +14259,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
+      <c r="D359" t="n">
+        <v>48</v>
       </c>
       <c r="E359" t="inlineStr">
         <is>
@@ -15000,10 +14284,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
+      <c r="D360" t="n">
+        <v>49.75</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
@@ -15027,10 +14309,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
+      <c r="D361" t="n">
+        <v>49.5</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
@@ -15054,10 +14334,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
+      <c r="D362" t="n">
+        <v>51</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
@@ -15081,10 +14359,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>53.75</t>
-        </is>
+      <c r="D363" t="n">
+        <v>53.75</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
@@ -15108,10 +14384,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>56.2</t>
-        </is>
+      <c r="D364" t="n">
+        <v>56.2</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
@@ -15135,10 +14409,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>56.5</t>
-        </is>
+      <c r="D365" t="n">
+        <v>56.5</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
@@ -15162,10 +14434,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>302.6</t>
-        </is>
+      <c r="D366" t="n">
+        <v>302.6</v>
       </c>
       <c r="E366" t="inlineStr">
         <is>
@@ -15189,10 +14459,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
+      <c r="D367" t="n">
+        <v>304</v>
       </c>
       <c r="E367" t="inlineStr">
         <is>
@@ -15216,10 +14484,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>300.5</t>
-        </is>
+      <c r="D368" t="n">
+        <v>300.5</v>
       </c>
       <c r="E368" t="inlineStr">
         <is>
@@ -15243,10 +14509,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>290.25</t>
-        </is>
+      <c r="D369" t="n">
+        <v>290.25</v>
       </c>
       <c r="E369" t="inlineStr">
         <is>
@@ -15270,10 +14534,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>282.2</t>
-        </is>
+      <c r="D370" t="n">
+        <v>282.2</v>
       </c>
       <c r="E370" t="inlineStr">
         <is>
@@ -15297,10 +14559,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>272.25</t>
-        </is>
+      <c r="D371" t="n">
+        <v>272.25</v>
       </c>
       <c r="E371" t="inlineStr">
         <is>
@@ -15324,10 +14584,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>263.25</t>
-        </is>
+      <c r="D372" t="n">
+        <v>263.25</v>
       </c>
       <c r="E372" t="inlineStr">
         <is>
@@ -15351,10 +14609,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
+      <c r="D373" t="n">
+        <v>256</v>
       </c>
       <c r="E373" t="inlineStr">
         <is>
@@ -15378,10 +14634,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>253.75</t>
-        </is>
+      <c r="D374" t="n">
+        <v>253.75</v>
       </c>
       <c r="E374" t="inlineStr">
         <is>
@@ -15405,10 +14659,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>250.6</t>
-        </is>
+      <c r="D375" t="n">
+        <v>250.6</v>
       </c>
       <c r="E375" t="inlineStr">
         <is>
@@ -15432,10 +14684,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>252.25</t>
-        </is>
+      <c r="D376" t="n">
+        <v>252.25</v>
       </c>
       <c r="E376" t="inlineStr">
         <is>
@@ -15459,10 +14709,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>248.25</t>
-        </is>
+      <c r="D377" t="n">
+        <v>248.25</v>
       </c>
       <c r="E377" t="inlineStr">
         <is>
@@ -15486,10 +14734,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>244.2</t>
-        </is>
+      <c r="D378" t="n">
+        <v>244.2</v>
       </c>
       <c r="E378" t="inlineStr">
         <is>
@@ -15513,10 +14759,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>239.5</t>
-        </is>
+      <c r="D379" t="n">
+        <v>239.5</v>
       </c>
       <c r="E379" t="inlineStr">
         <is>
@@ -15540,10 +14784,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>241.5</t>
-        </is>
+      <c r="D380" t="n">
+        <v>241.5</v>
       </c>
       <c r="E380" t="inlineStr">
         <is>
@@ -15567,10 +14809,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
+      <c r="D381" t="n">
+        <v>242</v>
       </c>
       <c r="E381" t="inlineStr">
         <is>
@@ -15594,10 +14834,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>246.8</t>
-        </is>
+      <c r="D382" t="n">
+        <v>246.8</v>
       </c>
       <c r="E382" t="inlineStr">
         <is>
@@ -15621,10 +14859,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>256.75</t>
-        </is>
+      <c r="D383" t="n">
+        <v>256.75</v>
       </c>
       <c r="E383" t="inlineStr">
         <is>
@@ -15648,10 +14884,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>258.8</t>
-        </is>
+      <c r="D384" t="n">
+        <v>258.8</v>
       </c>
       <c r="E384" t="inlineStr">
         <is>
@@ -15675,10 +14909,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>265.5</t>
-        </is>
+      <c r="D385" t="n">
+        <v>265.5</v>
       </c>
       <c r="E385" t="inlineStr">
         <is>
@@ -15702,10 +14934,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>.119</t>
-        </is>
+      <c r="D386" t="n">
+        <v>0.119</v>
       </c>
       <c r="E386" t="inlineStr">
         <is>
@@ -15734,10 +14964,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>.118</t>
-        </is>
+      <c r="D387" t="n">
+        <v>0.118</v>
       </c>
       <c r="E387" t="inlineStr">
         <is>
@@ -15766,10 +14994,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>.12</t>
-        </is>
+      <c r="D388" t="n">
+        <v>0.12</v>
       </c>
       <c r="E388" t="inlineStr">
         <is>
@@ -15798,10 +15024,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>.126</t>
-        </is>
+      <c r="D389" t="n">
+        <v>0.126</v>
       </c>
       <c r="E389" t="inlineStr">
         <is>
@@ -15830,10 +15054,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>.119</t>
-        </is>
+      <c r="D390" t="n">
+        <v>0.119</v>
       </c>
       <c r="E390" t="inlineStr">
         <is>
@@ -15862,10 +15084,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>.114</t>
-        </is>
+      <c r="D391" t="n">
+        <v>0.114</v>
       </c>
       <c r="E391" t="inlineStr">
         <is>
@@ -15894,10 +15114,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>.113</t>
-        </is>
+      <c r="D392" t="n">
+        <v>0.113</v>
       </c>
       <c r="E392" t="inlineStr">
         <is>
@@ -15926,10 +15144,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>.116</t>
-        </is>
+      <c r="D393" t="n">
+        <v>0.116</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
@@ -15958,10 +15174,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>.125</t>
-        </is>
+      <c r="D394" t="n">
+        <v>0.125</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
@@ -15990,10 +15204,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>.128</t>
-        </is>
+      <c r="D395" t="n">
+        <v>0.128</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
@@ -16022,10 +15234,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>.127</t>
-        </is>
+      <c r="D396" t="n">
+        <v>0.127</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
@@ -16054,10 +15264,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>.125</t>
-        </is>
+      <c r="D397" t="n">
+        <v>0.125</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
@@ -16086,10 +15294,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>.123</t>
-        </is>
+      <c r="D398" t="n">
+        <v>0.123</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
@@ -16118,10 +15324,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>.122</t>
-        </is>
+      <c r="D399" t="n">
+        <v>0.122</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
@@ -16150,10 +15354,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>.125</t>
-        </is>
+      <c r="D400" t="n">
+        <v>0.125</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
@@ -16182,10 +15384,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>.122</t>
-        </is>
+      <c r="D401" t="n">
+        <v>0.122</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
@@ -16214,10 +15414,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>.117</t>
-        </is>
+      <c r="D402" t="n">
+        <v>0.117</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
@@ -16246,10 +15444,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>.117</t>
-        </is>
+      <c r="D403" t="n">
+        <v>0.117</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
@@ -16278,10 +15474,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>.12</t>
-        </is>
+      <c r="D404" t="n">
+        <v>0.12</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
@@ -16310,10 +15504,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>.118</t>
-        </is>
+      <c r="D405" t="n">
+        <v>0.118</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
@@ -16342,10 +15534,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>1.212</t>
-        </is>
+      <c r="D406" t="n">
+        <v>1.212</v>
       </c>
       <c r="E406" t="inlineStr">
         <is>
@@ -16374,10 +15564,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>1.191</t>
-        </is>
+      <c r="D407" t="n">
+        <v>1.191</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
@@ -16406,10 +15594,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>1.223</t>
-        </is>
+      <c r="D408" t="n">
+        <v>1.223</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
@@ -16438,10 +15624,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>1.201</t>
-        </is>
+      <c r="D409" t="n">
+        <v>1.201</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
@@ -16470,10 +15654,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>1.159</t>
-        </is>
+      <c r="D410" t="n">
+        <v>1.159</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
@@ -16502,10 +15684,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr">
-        <is>
-          <t>1.203</t>
-        </is>
+      <c r="D411" t="n">
+        <v>1.203</v>
       </c>
       <c r="E411" t="inlineStr">
         <is>
@@ -16534,10 +15714,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr">
-        <is>
-          <t>1.217</t>
-        </is>
+      <c r="D412" t="n">
+        <v>1.217</v>
       </c>
       <c r="E412" t="inlineStr">
         <is>
@@ -16566,10 +15744,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>1.206</t>
-        </is>
+      <c r="D413" t="n">
+        <v>1.206</v>
       </c>
       <c r="E413" t="inlineStr">
         <is>
@@ -16598,10 +15774,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr">
-        <is>
-          <t>1.207</t>
-        </is>
+      <c r="D414" t="n">
+        <v>1.207</v>
       </c>
       <c r="E414" t="inlineStr">
         <is>
@@ -16630,10 +15804,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr">
-        <is>
-          <t>1.217</t>
-        </is>
+      <c r="D415" t="n">
+        <v>1.217</v>
       </c>
       <c r="E415" t="inlineStr">
         <is>
@@ -16662,10 +15834,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr">
-        <is>
-          <t>1.232</t>
-        </is>
+      <c r="D416" t="n">
+        <v>1.232</v>
       </c>
       <c r="E416" t="inlineStr">
         <is>
@@ -16694,10 +15864,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>1.162</t>
-        </is>
+      <c r="D417" t="n">
+        <v>1.162</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
@@ -16726,10 +15894,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>1.161</t>
-        </is>
+      <c r="D418" t="n">
+        <v>1.161</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
@@ -16758,10 +15924,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>1.166</t>
-        </is>
+      <c r="D419" t="n">
+        <v>1.166</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
@@ -16790,10 +15954,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>1.173</t>
-        </is>
+      <c r="D420" t="n">
+        <v>1.173</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
@@ -16822,10 +15984,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>1.175</t>
-        </is>
+      <c r="D421" t="n">
+        <v>1.175</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
@@ -16854,10 +16014,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>1.156</t>
-        </is>
+      <c r="D422" t="n">
+        <v>1.156</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
@@ -16886,10 +16044,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>1.179</t>
-        </is>
+      <c r="D423" t="n">
+        <v>1.179</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
@@ -16918,10 +16074,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr">
-        <is>
-          <t>1.183</t>
-        </is>
+      <c r="D424" t="n">
+        <v>1.183</v>
       </c>
       <c r="E424" t="inlineStr">
         <is>
@@ -16950,10 +16104,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>1.191</t>
-        </is>
+      <c r="D425" t="n">
+        <v>1.191</v>
       </c>
       <c r="E425" t="inlineStr">
         <is>
@@ -16982,10 +16134,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr">
-        <is>
-          <t>.981</t>
-        </is>
+      <c r="D426" t="n">
+        <v>0.981</v>
       </c>
       <c r="E426" t="inlineStr">
         <is>
@@ -17014,10 +16164,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
+      <c r="D427" t="n">
+        <v>1.04</v>
       </c>
       <c r="E427" t="inlineStr">
         <is>
@@ -17046,10 +16194,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>1.048</t>
-        </is>
+      <c r="D428" t="n">
+        <v>1.048</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
@@ -17078,10 +16224,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>1.055</t>
-        </is>
+      <c r="D429" t="n">
+        <v>1.055</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
@@ -17110,10 +16254,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr">
-        <is>
-          <t>1.059</t>
-        </is>
+      <c r="D430" t="n">
+        <v>1.059</v>
       </c>
       <c r="E430" t="inlineStr">
         <is>
@@ -17142,10 +16284,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>1.062</t>
-        </is>
+      <c r="D431" t="n">
+        <v>1.062</v>
       </c>
       <c r="E431" t="inlineStr">
         <is>
@@ -17174,10 +16314,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr">
-        <is>
-          <t>1.075</t>
-        </is>
+      <c r="D432" t="n">
+        <v>1.075</v>
       </c>
       <c r="E432" t="inlineStr">
         <is>
@@ -17206,10 +16344,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>1.051</t>
-        </is>
+      <c r="D433" t="n">
+        <v>1.051</v>
       </c>
       <c r="E433" t="inlineStr">
         <is>
@@ -17238,10 +16374,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr">
-        <is>
-          <t>1.005</t>
-        </is>
+      <c r="D434" t="n">
+        <v>1.005</v>
       </c>
       <c r="E434" t="inlineStr">
         <is>
@@ -17270,10 +16404,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>.97</t>
-        </is>
+      <c r="D435" t="n">
+        <v>0.97</v>
       </c>
       <c r="E435" t="inlineStr">
         <is>
@@ -17302,10 +16434,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>.984</t>
-        </is>
+      <c r="D436" t="n">
+        <v>0.984</v>
       </c>
       <c r="E436" t="inlineStr">
         <is>
@@ -17334,10 +16464,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr">
-        <is>
-          <t>.981</t>
-        </is>
+      <c r="D437" t="n">
+        <v>0.981</v>
       </c>
       <c r="E437" t="inlineStr">
         <is>
@@ -17366,10 +16494,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr">
-        <is>
-          <t>.991</t>
-        </is>
+      <c r="D438" t="n">
+        <v>0.991</v>
       </c>
       <c r="E438" t="inlineStr">
         <is>
@@ -17398,10 +16524,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>.99</t>
-        </is>
+      <c r="D439" t="n">
+        <v>0.99</v>
       </c>
       <c r="E439" t="inlineStr">
         <is>
@@ -17430,10 +16554,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr">
-        <is>
-          <t>.995</t>
-        </is>
+      <c r="D440" t="n">
+        <v>0.995</v>
       </c>
       <c r="E440" t="inlineStr">
         <is>
@@ -17462,10 +16584,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>1.011</t>
-        </is>
+      <c r="D441" t="n">
+        <v>1.011</v>
       </c>
       <c r="E441" t="inlineStr">
         <is>
@@ -17494,10 +16614,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>1.012</t>
-        </is>
+      <c r="D442" t="n">
+        <v>1.012</v>
       </c>
       <c r="E442" t="inlineStr">
         <is>
@@ -17526,10 +16644,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>.999</t>
-        </is>
+      <c r="D443" t="n">
+        <v>0.999</v>
       </c>
       <c r="E443" t="inlineStr">
         <is>
@@ -17558,10 +16674,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>1.005</t>
-        </is>
+      <c r="D444" t="n">
+        <v>1.005</v>
       </c>
       <c r="E444" t="inlineStr">
         <is>
@@ -17590,10 +16704,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>1.018</t>
-        </is>
+      <c r="D445" t="n">
+        <v>1.018</v>
       </c>
       <c r="E445" t="inlineStr">
         <is>
@@ -17622,10 +16734,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>9.002</t>
-        </is>
+      <c r="D446" t="n">
+        <v>9.002000000000001</v>
       </c>
       <c r="E446" t="inlineStr">
         <is>
@@ -17654,10 +16764,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>9.124</t>
-        </is>
+      <c r="D447" t="n">
+        <v>9.124000000000001</v>
       </c>
       <c r="E447" t="inlineStr">
         <is>
@@ -17686,10 +16794,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>9.35</t>
-        </is>
+      <c r="D448" t="n">
+        <v>9.35</v>
       </c>
       <c r="E448" t="inlineStr">
         <is>
@@ -17718,10 +16824,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>9.319</t>
-        </is>
+      <c r="D449" t="n">
+        <v>9.319000000000001</v>
       </c>
       <c r="E449" t="inlineStr">
         <is>
@@ -17750,10 +16854,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>9.309</t>
-        </is>
+      <c r="D450" t="n">
+        <v>9.308999999999999</v>
       </c>
       <c r="E450" t="inlineStr">
         <is>
@@ -17782,10 +16884,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>9.346</t>
-        </is>
+      <c r="D451" t="n">
+        <v>9.346</v>
       </c>
       <c r="E451" t="inlineStr">
         <is>
@@ -17814,10 +16914,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>9.475</t>
-        </is>
+      <c r="D452" t="n">
+        <v>9.475</v>
       </c>
       <c r="E452" t="inlineStr">
         <is>
@@ -17846,10 +16944,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr">
-        <is>
-          <t>9.452</t>
-        </is>
+      <c r="D453" t="n">
+        <v>9.452</v>
       </c>
       <c r="E453" t="inlineStr">
         <is>
@@ -17878,10 +16974,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr">
-        <is>
-          <t>9.452</t>
-        </is>
+      <c r="D454" t="n">
+        <v>9.452</v>
       </c>
       <c r="E454" t="inlineStr">
         <is>
@@ -17910,10 +17004,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>9.459</t>
-        </is>
+      <c r="D455" t="n">
+        <v>9.459</v>
       </c>
       <c r="E455" t="inlineStr">
         <is>
@@ -17942,10 +17034,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>9.492</t>
-        </is>
+      <c r="D456" t="n">
+        <v>9.492000000000001</v>
       </c>
       <c r="E456" t="inlineStr">
         <is>
@@ -17974,10 +17064,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>9.355</t>
-        </is>
+      <c r="D457" t="n">
+        <v>9.355</v>
       </c>
       <c r="E457" t="inlineStr">
         <is>
@@ -18006,10 +17094,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>8.975</t>
-        </is>
+      <c r="D458" t="n">
+        <v>8.975</v>
       </c>
       <c r="E458" t="inlineStr">
         <is>
@@ -18038,10 +17124,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>9.387</t>
-        </is>
+      <c r="D459" t="n">
+        <v>9.387</v>
       </c>
       <c r="E459" t="inlineStr">
         <is>
@@ -18070,10 +17154,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>9.444</t>
-        </is>
+      <c r="D460" t="n">
+        <v>9.444000000000001</v>
       </c>
       <c r="E460" t="inlineStr">
         <is>
@@ -18102,10 +17184,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>9.464</t>
-        </is>
+      <c r="D461" t="n">
+        <v>9.464</v>
       </c>
       <c r="E461" t="inlineStr">
         <is>
@@ -18134,10 +17214,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>9.455</t>
-        </is>
+      <c r="D462" t="n">
+        <v>9.455</v>
       </c>
       <c r="E462" t="inlineStr">
         <is>
@@ -18166,10 +17244,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>9.38</t>
-        </is>
+      <c r="D463" t="n">
+        <v>9.380000000000001</v>
       </c>
       <c r="E463" t="inlineStr">
         <is>
@@ -18198,10 +17274,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>9.495</t>
-        </is>
+      <c r="D464" t="n">
+        <v>9.494999999999999</v>
       </c>
       <c r="E464" t="inlineStr">
         <is>
@@ -18230,10 +17304,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr">
-        <is>
-          <t>9.5</t>
-        </is>
+      <c r="D465" t="n">
+        <v>9.5</v>
       </c>
       <c r="E465" t="inlineStr">
         <is>
@@ -18262,10 +17334,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr">
-        <is>
-          <t>.113</t>
-        </is>
+      <c r="D466" t="n">
+        <v>0.113</v>
       </c>
       <c r="E466" t="inlineStr">
         <is>
@@ -18294,10 +17364,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr">
-        <is>
-          <t>.103</t>
-        </is>
+      <c r="D467" t="n">
+        <v>0.103</v>
       </c>
       <c r="E467" t="inlineStr">
         <is>
@@ -18326,10 +17394,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr">
-        <is>
-          <t>.12</t>
-        </is>
+      <c r="D468" t="n">
+        <v>0.12</v>
       </c>
       <c r="E468" t="inlineStr">
         <is>
@@ -18358,10 +17424,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr">
-        <is>
-          <t>.118</t>
-        </is>
+      <c r="D469" t="n">
+        <v>0.118</v>
       </c>
       <c r="E469" t="inlineStr">
         <is>
@@ -18390,10 +17454,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr">
-        <is>
-          <t>.119</t>
-        </is>
+      <c r="D470" t="n">
+        <v>0.119</v>
       </c>
       <c r="E470" t="inlineStr">
         <is>
@@ -18422,10 +17484,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr">
-        <is>
-          <t>.121</t>
-        </is>
+      <c r="D471" t="n">
+        <v>0.121</v>
       </c>
       <c r="E471" t="inlineStr">
         <is>
@@ -18454,10 +17514,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr">
-        <is>
-          <t>.121</t>
-        </is>
+      <c r="D472" t="n">
+        <v>0.121</v>
       </c>
       <c r="E472" t="inlineStr">
         <is>
@@ -18486,10 +17544,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr">
-        <is>
-          <t>.115</t>
-        </is>
+      <c r="D473" t="n">
+        <v>0.115</v>
       </c>
       <c r="E473" t="inlineStr">
         <is>
@@ -18518,10 +17574,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr">
-        <is>
-          <t>.118</t>
-        </is>
+      <c r="D474" t="n">
+        <v>0.118</v>
       </c>
       <c r="E474" t="inlineStr">
         <is>
@@ -18550,10 +17604,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr">
-        <is>
-          <t>.121</t>
-        </is>
+      <c r="D475" t="n">
+        <v>0.121</v>
       </c>
       <c r="E475" t="inlineStr">
         <is>
@@ -18582,10 +17634,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr">
-        <is>
-          <t>.117</t>
-        </is>
+      <c r="D476" t="n">
+        <v>0.117</v>
       </c>
       <c r="E476" t="inlineStr">
         <is>
@@ -18614,10 +17664,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr">
-        <is>
-          <t>.113</t>
-        </is>
+      <c r="D477" t="n">
+        <v>0.113</v>
       </c>
       <c r="E477" t="inlineStr">
         <is>
@@ -18646,10 +17694,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr">
-        <is>
-          <t>.098</t>
-        </is>
+      <c r="D478" t="n">
+        <v>0.098</v>
       </c>
       <c r="E478" t="inlineStr">
         <is>
@@ -18678,10 +17724,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr">
-        <is>
-          <t>.11</t>
-        </is>
+      <c r="D479" t="n">
+        <v>0.11</v>
       </c>
       <c r="E479" t="inlineStr">
         <is>
@@ -18710,10 +17754,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr">
-        <is>
-          <t>.105</t>
-        </is>
+      <c r="D480" t="n">
+        <v>0.105</v>
       </c>
       <c r="E480" t="inlineStr">
         <is>
@@ -18742,10 +17784,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr">
-        <is>
-          <t>.098</t>
-        </is>
+      <c r="D481" t="n">
+        <v>0.098</v>
       </c>
       <c r="E481" t="inlineStr">
         <is>
@@ -18774,10 +17814,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr">
-        <is>
-          <t>.1</t>
-        </is>
+      <c r="D482" t="n">
+        <v>0.1</v>
       </c>
       <c r="E482" t="inlineStr">
         <is>
@@ -18806,10 +17844,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>.098</t>
-        </is>
+      <c r="D483" t="n">
+        <v>0.098</v>
       </c>
       <c r="E483" t="inlineStr">
         <is>
@@ -18838,10 +17874,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>.096</t>
-        </is>
+      <c r="D484" t="n">
+        <v>0.096</v>
       </c>
       <c r="E484" t="inlineStr">
         <is>
@@ -18870,10 +17904,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>.094</t>
-        </is>
+      <c r="D485" t="n">
+        <v>0.094</v>
       </c>
       <c r="E485" t="inlineStr">
         <is>
@@ -18902,10 +17934,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr">
-        <is>
-          <t>.477</t>
-        </is>
+      <c r="D486" t="n">
+        <v>0.477</v>
       </c>
       <c r="E486" t="inlineStr">
         <is>
@@ -18934,10 +17964,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr">
-        <is>
-          <t>.471</t>
-        </is>
+      <c r="D487" t="n">
+        <v>0.471</v>
       </c>
       <c r="E487" t="inlineStr">
         <is>
@@ -18966,10 +17994,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr">
-        <is>
-          <t>.475</t>
-        </is>
+      <c r="D488" t="n">
+        <v>0.475</v>
       </c>
       <c r="E488" t="inlineStr">
         <is>
@@ -18998,10 +18024,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>.454</t>
-        </is>
+      <c r="D489" t="n">
+        <v>0.454</v>
       </c>
       <c r="E489" t="inlineStr">
         <is>
@@ -19030,10 +18054,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr">
-        <is>
-          <t>.475</t>
-        </is>
+      <c r="D490" t="n">
+        <v>0.475</v>
       </c>
       <c r="E490" t="inlineStr">
         <is>
@@ -19062,10 +18084,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr">
-        <is>
-          <t>.454</t>
-        </is>
+      <c r="D491" t="n">
+        <v>0.454</v>
       </c>
       <c r="E491" t="inlineStr">
         <is>
@@ -19094,10 +18114,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr">
-        <is>
-          <t>.465</t>
-        </is>
+      <c r="D492" t="n">
+        <v>0.465</v>
       </c>
       <c r="E492" t="inlineStr">
         <is>
@@ -19126,10 +18144,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr">
-        <is>
-          <t>.467</t>
-        </is>
+      <c r="D493" t="n">
+        <v>0.467</v>
       </c>
       <c r="E493" t="inlineStr">
         <is>
@@ -19158,10 +18174,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr">
-        <is>
-          <t>.463</t>
-        </is>
+      <c r="D494" t="n">
+        <v>0.463</v>
       </c>
       <c r="E494" t="inlineStr">
         <is>
@@ -19190,10 +18204,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr">
-        <is>
-          <t>.472</t>
-        </is>
+      <c r="D495" t="n">
+        <v>0.472</v>
       </c>
       <c r="E495" t="inlineStr">
         <is>
@@ -19222,10 +18234,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr">
-        <is>
-          <t>.461</t>
-        </is>
+      <c r="D496" t="n">
+        <v>0.461</v>
       </c>
       <c r="E496" t="inlineStr">
         <is>
@@ -19254,10 +18264,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr">
-        <is>
-          <t>.448</t>
-        </is>
+      <c r="D497" t="n">
+        <v>0.448</v>
       </c>
       <c r="E497" t="inlineStr">
         <is>
@@ -19286,10 +18294,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>.434</t>
-        </is>
+      <c r="D498" t="n">
+        <v>0.434</v>
       </c>
       <c r="E498" t="inlineStr">
         <is>
@@ -19318,10 +18324,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr">
-        <is>
-          <t>.441</t>
-        </is>
+      <c r="D499" t="n">
+        <v>0.441</v>
       </c>
       <c r="E499" t="inlineStr">
         <is>
@@ -19350,10 +18354,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr">
-        <is>
-          <t>.452</t>
-        </is>
+      <c r="D500" t="n">
+        <v>0.452</v>
       </c>
       <c r="E500" t="inlineStr">
         <is>
@@ -19382,10 +18384,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr">
-        <is>
-          <t>.45</t>
-        </is>
+      <c r="D501" t="n">
+        <v>0.45</v>
       </c>
       <c r="E501" t="inlineStr">
         <is>
@@ -19414,10 +18414,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr">
-        <is>
-          <t>.437</t>
-        </is>
+      <c r="D502" t="n">
+        <v>0.437</v>
       </c>
       <c r="E502" t="inlineStr">
         <is>
@@ -19446,10 +18444,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>.43</t>
-        </is>
+      <c r="D503" t="n">
+        <v>0.43</v>
       </c>
       <c r="E503" t="inlineStr">
         <is>
@@ -19478,10 +18474,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr">
-        <is>
-          <t>.435</t>
-        </is>
+      <c r="D504" t="n">
+        <v>0.435</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
@@ -19510,10 +18504,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr">
-        <is>
-          <t>.443</t>
-        </is>
+      <c r="D505" t="n">
+        <v>0.443</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
@@ -19542,10 +18534,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr">
-        <is>
-          <t>5.667</t>
-        </is>
+      <c r="D506" t="n">
+        <v>5.667</v>
       </c>
       <c r="E506" t="inlineStr">
         <is>
@@ -19574,10 +18564,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr">
-        <is>
-          <t>5.763</t>
-        </is>
+      <c r="D507" t="n">
+        <v>5.763</v>
       </c>
       <c r="E507" t="inlineStr">
         <is>
@@ -19606,10 +18594,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr">
-        <is>
-          <t>5.906</t>
-        </is>
+      <c r="D508" t="n">
+        <v>5.906</v>
       </c>
       <c r="E508" t="inlineStr">
         <is>
@@ -19638,10 +18624,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>5.922</t>
-        </is>
+      <c r="D509" t="n">
+        <v>5.922</v>
       </c>
       <c r="E509" t="inlineStr">
         <is>
@@ -19670,10 +18654,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr">
-        <is>
-          <t>5.919</t>
-        </is>
+      <c r="D510" t="n">
+        <v>5.919</v>
       </c>
       <c r="E510" t="inlineStr">
         <is>
@@ -19702,10 +18684,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr">
-        <is>
-          <t>5.926</t>
-        </is>
+      <c r="D511" t="n">
+        <v>5.926</v>
       </c>
       <c r="E511" t="inlineStr">
         <is>
@@ -19734,10 +18714,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr">
-        <is>
-          <t>6.034</t>
-        </is>
+      <c r="D512" t="n">
+        <v>6.034</v>
       </c>
       <c r="E512" t="inlineStr">
         <is>
@@ -19766,10 +18744,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr">
-        <is>
-          <t>6.035</t>
-        </is>
+      <c r="D513" t="n">
+        <v>6.035</v>
       </c>
       <c r="E513" t="inlineStr">
         <is>
@@ -19798,10 +18774,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr">
-        <is>
-          <t>6.072</t>
-        </is>
+      <c r="D514" t="n">
+        <v>6.072</v>
       </c>
       <c r="E514" t="inlineStr">
         <is>
@@ -19830,10 +18804,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>6.118</t>
-        </is>
+      <c r="D515" t="n">
+        <v>6.118</v>
       </c>
       <c r="E515" t="inlineStr">
         <is>
@@ -19862,10 +18834,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>6.142</t>
-        </is>
+      <c r="D516" t="n">
+        <v>6.142</v>
       </c>
       <c r="E516" t="inlineStr">
         <is>
@@ -19894,10 +18864,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>6.081</t>
-        </is>
+      <c r="D517" t="n">
+        <v>6.081</v>
       </c>
       <c r="E517" t="inlineStr">
         <is>
@@ -19926,10 +18894,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr">
-        <is>
-          <t>5.756</t>
-        </is>
+      <c r="D518" t="n">
+        <v>5.756</v>
       </c>
       <c r="E518" t="inlineStr">
         <is>
@@ -19958,10 +18924,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr">
-        <is>
-          <t>6.125</t>
-        </is>
+      <c r="D519" t="n">
+        <v>6.125</v>
       </c>
       <c r="E519" t="inlineStr">
         <is>
@@ -19990,10 +18954,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr">
-        <is>
-          <t>6.15</t>
-        </is>
+      <c r="D520" t="n">
+        <v>6.15</v>
       </c>
       <c r="E520" t="inlineStr">
         <is>
@@ -20022,10 +18984,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr">
-        <is>
-          <t>6.165</t>
-        </is>
+      <c r="D521" t="n">
+        <v>6.165</v>
       </c>
       <c r="E521" t="inlineStr">
         <is>
@@ -20054,10 +19014,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr">
-        <is>
-          <t>6.177</t>
-        </is>
+      <c r="D522" t="n">
+        <v>6.177</v>
       </c>
       <c r="E522" t="inlineStr">
         <is>
@@ -20086,10 +19044,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr">
-        <is>
-          <t>6.097</t>
-        </is>
+      <c r="D523" t="n">
+        <v>6.097</v>
       </c>
       <c r="E523" t="inlineStr">
         <is>
@@ -20118,10 +19074,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr">
-        <is>
-          <t>6.204</t>
-        </is>
+      <c r="D524" t="n">
+        <v>6.204</v>
       </c>
       <c r="E524" t="inlineStr">
         <is>
@@ -20150,10 +19104,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>6.176</t>
-        </is>
+      <c r="D525" t="n">
+        <v>6.176</v>
       </c>
       <c r="E525" t="inlineStr">
         <is>
@@ -20182,10 +19134,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr">
-        <is>
-          <t>.343</t>
-        </is>
+      <c r="D526" t="n">
+        <v>0.343</v>
       </c>
       <c r="E526" t="inlineStr">
         <is>
@@ -20214,10 +19164,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D527" t="inlineStr">
-        <is>
-          <t>.355</t>
-        </is>
+      <c r="D527" t="n">
+        <v>0.355</v>
       </c>
       <c r="E527" t="inlineStr">
         <is>
@@ -20246,10 +19194,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D528" t="inlineStr">
-        <is>
-          <t>.373</t>
-        </is>
+      <c r="D528" t="n">
+        <v>0.373</v>
       </c>
       <c r="E528" t="inlineStr">
         <is>
@@ -20278,10 +19224,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>.363</t>
-        </is>
+      <c r="D529" t="n">
+        <v>0.363</v>
       </c>
       <c r="E529" t="inlineStr">
         <is>
@@ -20310,10 +19254,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>.379</t>
-        </is>
+      <c r="D530" t="n">
+        <v>0.379</v>
       </c>
       <c r="E530" t="inlineStr">
         <is>
@@ -20342,10 +19284,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D531" t="inlineStr">
-        <is>
-          <t>.386</t>
-        </is>
+      <c r="D531" t="n">
+        <v>0.386</v>
       </c>
       <c r="E531" t="inlineStr">
         <is>
@@ -20374,10 +19314,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D532" t="inlineStr">
-        <is>
-          <t>.37</t>
-        </is>
+      <c r="D532" t="n">
+        <v>0.37</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
@@ -20406,10 +19344,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr">
-        <is>
-          <t>.384</t>
-        </is>
+      <c r="D533" t="n">
+        <v>0.384</v>
       </c>
       <c r="E533" t="inlineStr">
         <is>
@@ -20438,10 +19374,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D534" t="inlineStr">
-        <is>
-          <t>.385</t>
-        </is>
+      <c r="D534" t="n">
+        <v>0.385</v>
       </c>
       <c r="E534" t="inlineStr">
         <is>
@@ -20470,10 +19404,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D535" t="inlineStr">
-        <is>
-          <t>.354</t>
-        </is>
+      <c r="D535" t="n">
+        <v>0.354</v>
       </c>
       <c r="E535" t="inlineStr">
         <is>
@@ -20502,10 +19434,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr">
-        <is>
-          <t>.351</t>
-        </is>
+      <c r="D536" t="n">
+        <v>0.351</v>
       </c>
       <c r="E536" t="inlineStr">
         <is>
@@ -20534,10 +19464,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D537" t="inlineStr">
-        <is>
-          <t>.367</t>
-        </is>
+      <c r="D537" t="n">
+        <v>0.367</v>
       </c>
       <c r="E537" t="inlineStr">
         <is>
@@ -20566,10 +19494,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D538" t="inlineStr">
-        <is>
-          <t>.343</t>
-        </is>
+      <c r="D538" t="n">
+        <v>0.343</v>
       </c>
       <c r="E538" t="inlineStr">
         <is>
@@ -20598,10 +19524,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr">
-        <is>
-          <t>.36</t>
-        </is>
+      <c r="D539" t="n">
+        <v>0.36</v>
       </c>
       <c r="E539" t="inlineStr">
         <is>
@@ -20630,10 +19554,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr">
-        <is>
-          <t>.369</t>
-        </is>
+      <c r="D540" t="n">
+        <v>0.369</v>
       </c>
       <c r="E540" t="inlineStr">
         <is>
@@ -20662,10 +19584,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D541" t="inlineStr">
-        <is>
-          <t>.366</t>
-        </is>
+      <c r="D541" t="n">
+        <v>0.366</v>
       </c>
       <c r="E541" t="inlineStr">
         <is>
@@ -20694,10 +19614,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D542" t="inlineStr">
-        <is>
-          <t>.375</t>
-        </is>
+      <c r="D542" t="n">
+        <v>0.375</v>
       </c>
       <c r="E542" t="inlineStr">
         <is>
@@ -20726,10 +19644,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D543" t="inlineStr">
-        <is>
-          <t>.38</t>
-        </is>
+      <c r="D543" t="n">
+        <v>0.38</v>
       </c>
       <c r="E543" t="inlineStr">
         <is>
@@ -20758,10 +19674,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>.372</t>
-        </is>
+      <c r="D544" t="n">
+        <v>0.372</v>
       </c>
       <c r="E544" t="inlineStr">
         <is>
@@ -20790,10 +19704,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D545" t="inlineStr">
-        <is>
-          <t>.38</t>
-        </is>
+      <c r="D545" t="n">
+        <v>0.38</v>
       </c>
       <c r="E545" t="inlineStr">
         <is>
@@ -20822,10 +19734,8 @@
           <t>2025-01</t>
         </is>
       </c>
-      <c r="D546" t="inlineStr">
-        <is>
-          <t>.09</t>
-        </is>
+      <c r="D546" t="n">
+        <v>0.09</v>
       </c>
       <c r="E546" t="inlineStr">
         <is>
@@ -20854,10 +19764,8 @@
           <t>2025-02</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr">
-        <is>
-          <t>.083</t>
-        </is>
+      <c r="D547" t="n">
+        <v>0.083</v>
       </c>
       <c r="E547" t="inlineStr">
         <is>
@@ -20886,10 +19794,8 @@
           <t>2025-03</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr">
-        <is>
-          <t>.085</t>
-        </is>
+      <c r="D548" t="n">
+        <v>0.08500000000000001</v>
       </c>
       <c r="E548" t="inlineStr">
         <is>
@@ -20918,10 +19824,8 @@
           <t>2025-04</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr">
-        <is>
-          <t>.08</t>
-        </is>
+      <c r="D549" t="n">
+        <v>0.08</v>
       </c>
       <c r="E549" t="inlineStr">
         <is>
@@ -20950,10 +19854,8 @@
           <t>2025-05</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr">
-        <is>
-          <t>.08</t>
-        </is>
+      <c r="D550" t="n">
+        <v>0.08</v>
       </c>
       <c r="E550" t="inlineStr">
         <is>
@@ -20982,10 +19884,8 @@
           <t>2025-06</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr">
-        <is>
-          <t>.08</t>
-        </is>
+      <c r="D551" t="n">
+        <v>0.08</v>
       </c>
       <c r="E551" t="inlineStr">
         <is>
@@ -21014,10 +19914,8 @@
           <t>2025-07</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr">
-        <is>
-          <t>.08</t>
-        </is>
+      <c r="D552" t="n">
+        <v>0.08</v>
       </c>
       <c r="E552" t="inlineStr">
         <is>
@@ -21046,10 +19944,8 @@
           <t>2025-08</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>.078</t>
-        </is>
+      <c r="D553" t="n">
+        <v>0.078</v>
       </c>
       <c r="E553" t="inlineStr">
         <is>
@@ -21078,10 +19974,8 @@
           <t>2025-09</t>
         </is>
       </c>
-      <c r="D554" t="inlineStr">
-        <is>
-          <t>.077</t>
-        </is>
+      <c r="D554" t="n">
+        <v>0.077</v>
       </c>
       <c r="E554" t="inlineStr">
         <is>
@@ -21110,10 +20004,8 @@
           <t>2025-10</t>
         </is>
       </c>
-      <c r="D555" t="inlineStr">
-        <is>
-          <t>.079</t>
-        </is>
+      <c r="D555" t="n">
+        <v>0.079</v>
       </c>
       <c r="E555" t="inlineStr">
         <is>
@@ -21142,10 +20034,8 @@
           <t>2025-11</t>
         </is>
       </c>
-      <c r="D556" t="inlineStr">
-        <is>
-          <t>.078</t>
-        </is>
+      <c r="D556" t="n">
+        <v>0.078</v>
       </c>
       <c r="E556" t="inlineStr">
         <is>
@@ -21174,10 +20064,8 @@
           <t>2025-12</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr">
-        <is>
-          <t>.078</t>
-        </is>
+      <c r="D557" t="n">
+        <v>0.078</v>
       </c>
       <c r="E557" t="inlineStr">
         <is>
@@ -21206,10 +20094,8 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="D558" t="inlineStr">
-        <is>
-          <t>.069</t>
-        </is>
+      <c r="D558" t="n">
+        <v>0.06900000000000001</v>
       </c>
       <c r="E558" t="inlineStr">
         <is>
@@ -21238,10 +20124,8 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="D559" t="inlineStr">
-        <is>
-          <t>.073</t>
-        </is>
+      <c r="D559" t="n">
+        <v>0.073</v>
       </c>
       <c r="E559" t="inlineStr">
         <is>
@@ -21270,10 +20154,8 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="D560" t="inlineStr">
-        <is>
-          <t>.075</t>
-        </is>
+      <c r="D560" t="n">
+        <v>0.075</v>
       </c>
       <c r="E560" t="inlineStr">
         <is>
@@ -21302,10 +20184,8 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr">
-        <is>
-          <t>.077</t>
-        </is>
+      <c r="D561" t="n">
+        <v>0.077</v>
       </c>
       <c r="E561" t="inlineStr">
         <is>
@@ -21334,10 +20214,8 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="D562" t="inlineStr">
-        <is>
-          <t>.081</t>
-        </is>
+      <c r="D562" t="n">
+        <v>0.081</v>
       </c>
       <c r="E562" t="inlineStr">
         <is>
@@ -21366,10 +20244,8 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="D563" t="inlineStr">
-        <is>
-          <t>.08</t>
-        </is>
+      <c r="D563" t="n">
+        <v>0.08</v>
       </c>
       <c r="E563" t="inlineStr">
         <is>
@@ -21398,10 +20274,8 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="D564" t="inlineStr">
-        <is>
-          <t>.08</t>
-        </is>
+      <c r="D564" t="n">
+        <v>0.08</v>
       </c>
       <c r="E564" t="inlineStr">
         <is>
@@ -21430,10 +20304,8 @@
           <t>2026-08</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr">
-        <is>
-          <t>.08</t>
-        </is>
+      <c r="D565" t="n">
+        <v>0.08</v>
       </c>
       <c r="E565" t="inlineStr">
         <is>

--- a/output/Data and Chart Outputs/oil_cost_curve.xlsx
+++ b/output/Data and Chart Outputs/oil_cost_curve.xlsx
@@ -22009,11 +22009,11 @@
         </is>
       </c>
       <c r="C14" s="5">
-        <f>SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"COPRPM|"&amp;$B$5)</f>
+        <f>SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"COPRPM|"&amp;$B$5)</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>-SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"COEOPPM|"&amp;$B$5)/1000</f>
+        <f>-SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"COEOPPM|"&amp;$B$5)/1000</f>
         <v/>
       </c>
       <c r="E14" s="4" t="n">
@@ -22040,7 +22040,7 @@
         <v>65000</v>
       </c>
       <c r="N14">
-        <f>SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"NWCPM|"&amp;$B$5)*12</f>
+        <f>SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"NWCPM|"&amp;$B$5)*12</f>
         <v/>
       </c>
       <c r="O14" s="6">
@@ -22074,11 +22074,11 @@
         </is>
       </c>
       <c r="C15" s="5">
-        <f>SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"COPRBK|"&amp;$B$5)</f>
+        <f>SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"COPRBK|"&amp;$B$5)</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>-SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"COEOPBK|"&amp;$B$5)/1000</f>
+        <f>-SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"COEOPBK|"&amp;$B$5)/1000</f>
         <v/>
       </c>
       <c r="E15" s="4" t="n">
@@ -22105,7 +22105,7 @@
         <v>5000</v>
       </c>
       <c r="N15">
-        <f>SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"NWCBK|"&amp;$B$5)*12</f>
+        <f>SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"NWCBK|"&amp;$B$5)*12</f>
         <v/>
       </c>
       <c r="O15" s="6">
@@ -22139,11 +22139,11 @@
         </is>
       </c>
       <c r="C16" s="5">
-        <f>SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"COPREF|"&amp;$B$5)</f>
+        <f>SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"COPREF|"&amp;$B$5)</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>-SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"COEOPEF|"&amp;$B$5)/1000</f>
+        <f>-SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"COEOPEF|"&amp;$B$5)/1000</f>
         <v/>
       </c>
       <c r="E16" s="4" t="n">
@@ -22170,7 +22170,7 @@
         <v>13000</v>
       </c>
       <c r="N16">
-        <f>SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"NWCEF|"&amp;$B$5)*12</f>
+        <f>SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"NWCEF|"&amp;$B$5)*12</f>
         <v/>
       </c>
       <c r="O16" s="6">
@@ -22204,7 +22204,7 @@
         </is>
       </c>
       <c r="C17" s="5">
-        <f>SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"TOPRL48|"&amp;$B$5)-SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"TOPRPM|"&amp;$B$5)-SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"TOPRBK|"&amp;$B$5)-SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"TOPREF|"&amp;$B$5)</f>
+        <f>SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"TOPRL48|"&amp;$B$5)-SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"TOPRPM|"&amp;$B$5)-SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"TOPRBK|"&amp;$B$5)-SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"TOPREF|"&amp;$B$5)</f>
         <v/>
       </c>
       <c r="D17" s="5">

--- a/output/Data and Chart Outputs/oil_cost_curve.xlsx
+++ b/output/Data and Chart Outputs/oil_cost_curve.xlsx
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="R14" s="5">
-        <f>SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"COPRPM|"&amp;$B$10)-C14</f>
+        <f>SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"COPRPM|"&amp;$B$10)-C14</f>
         <v/>
       </c>
     </row>
@@ -22123,7 +22123,7 @@
         </is>
       </c>
       <c r="R15" s="5">
-        <f>SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"COPRBK|"&amp;$B$10)-C15</f>
+        <f>SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"COPRBK|"&amp;$B$10)-C15</f>
         <v/>
       </c>
     </row>
@@ -22188,7 +22188,7 @@
         </is>
       </c>
       <c r="R16" s="5">
-        <f>SUMIFS('STEO raw'!$E:$E,'STEO raw'!$A:$A,"COPREF|"&amp;$B$10)-C16</f>
+        <f>SUMIFS('STEO raw'!$D:$D,'STEO raw'!$A:$A,"COPREF|"&amp;$B$10)-C16</f>
         <v/>
       </c>
     </row>
